--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -9443,7 +9443,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -14334,7 +14334,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -14669,7 +14669,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -16679,7 +16679,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -18086,7 +18086,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -18220,7 +18220,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -18421,7 +18421,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -18488,7 +18488,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -18555,7 +18555,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -22307,7 +22307,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -22374,7 +22374,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -23446,7 +23446,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -23647,7 +23647,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -24612,7 +24612,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -25232,7 +25232,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -25294,7 +25294,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -52049,7 +52049,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UF1</t>
+          <t>Sisga - Guateque</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -52059,11 +52059,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34+258</t>
-        </is>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
+          <t>49+000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -52074,21 +52076,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UF2</t>
+          <t>Guateque - Macanal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34+258</t>
+          <t>49+000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>68+515</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
+          <t>71+000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -52099,21 +52103,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UF3</t>
+          <t>Macanal - Santa Maria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>68+515</t>
+          <t>71+000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>102+773</t>
-        </is>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
+          <t>89+000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -52124,21 +52130,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UF4</t>
+          <t>Santa Maria - San Luis de Gaceno - Aguaclara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>102+773</t>
+          <t>89+000</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>137+030</t>
-        </is>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
+          <t>136+000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -723,7 +723,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    137,03 km del corredor. Ponga los tramos reales.</t>
+          <t xml:space="preserve">    137,17 km del corredor. Ponga los tramos reales.</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -16813,7 +16813,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -22977,7 +22977,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -52049,7 +52049,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sisga - Guateque</t>
+          <t>Sisga - Macheta - Manta - Guateque</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -52059,7 +52059,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49+000</t>
+          <t>50+010</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -52076,17 +52076,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Guateque - Macanal</t>
+          <t>Guateque - Garagoa - Macanal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49+000</t>
+          <t>50+010</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>71+000</t>
+          <t>72+010</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -52108,12 +52108,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>71+000</t>
+          <t>72+010</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>89+000</t>
+          <t>89+810</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -52130,17 +52130,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Santa Maria - San Luis de Gaceno - Aguaclara</t>
+          <t>Santa Maria - Cachipay - San Luis de Gaceno - Aguaclara</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>89+000</t>
+          <t>89+810</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>136+000</t>
+          <t>137+170</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -26422,7 +26422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26459,6 +26459,164 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CCO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sutatenza</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Peaje Macheta</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Macheta</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>27+240</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Peaje SLG</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>San Luis de Gaceno</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bascula Macheta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Macheta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bascula SLG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>San Luis de Gaceno</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -1341,7 +1341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,23 +1403,6 @@
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CAL-04</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Separador</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -24609,7 +24592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24801,180 +24784,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SED-007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CCO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sutatenza</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>SED-008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Bogota</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bogota</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SED-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Peaje Macheta</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Macheta</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>UNF-01</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>27+240</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>5607</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SED-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Peaje SLG</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Luis de Gaceno</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SED-011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bascula Macheta</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Macheta</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SED-012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bascula SLG</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Luis de Gaceno</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -1372,8 +1372,10 @@
           <t>Izquierda</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1387,8 +1389,10 @@
           <t>Derecha</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1621,6 +1625,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5.099798, -73.718568</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>00+100</t>
@@ -1683,6 +1692,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5.098955, -73.714034</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>01+101</t>
@@ -1745,6 +1759,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5.099005, -73.711077</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>02+101</t>
@@ -1807,6 +1826,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5.099430, -73.718723</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>00+101</t>
@@ -1869,6 +1893,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5.098192, -73.713733</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>01+102</t>
@@ -1931,6 +1960,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5.097546, -73.710097</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>02+102</t>
@@ -1993,6 +2027,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5.100879, -73.719967</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>00+102</t>
@@ -2055,6 +2094,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5.098055, -73.713418</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>01+103</t>
@@ -2117,6 +2161,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5.099056, -73.709642</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>02+103</t>
@@ -2179,6 +2228,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5.100245, -73.719408</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>00+103</t>
@@ -2241,6 +2295,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5.099781, -73.714234</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>01+104</t>
@@ -2303,6 +2362,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5.097841, -73.709195</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>02+104</t>
@@ -2365,6 +2429,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5.099145, -73.718626</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>00+104</t>
@@ -2427,6 +2496,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5.098919, -73.714717</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>01+105</t>
@@ -2489,6 +2563,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5.097364, -73.710501</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>02+105</t>
@@ -2551,6 +2630,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5.100317, -73.720309</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>00+105</t>
@@ -2613,6 +2697,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5.098995, -73.713475</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>01+106</t>
@@ -2675,6 +2764,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5.099183, -73.709291</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>02+106</t>
@@ -2737,6 +2831,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5.099442, -73.720088</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
           <t>00+106</t>
@@ -2799,6 +2898,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5.099157, -73.713992</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>01+107</t>
@@ -2861,6 +2965,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5.097863, -73.708917</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>02+107</t>
@@ -2923,6 +3032,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5.100165, -73.718864</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
           <t>00+107</t>
@@ -2985,6 +3099,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5.097965, -73.714980</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>01+108</t>
@@ -3047,6 +3166,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5.097111, -73.709098</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
           <t>02+108</t>
@@ -3109,6 +3233,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5.099958, -73.720246</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>00+108</t>
@@ -3171,6 +3300,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5.100173, -73.713801</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>01+109</t>
@@ -3233,6 +3367,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5.098548, -73.710781</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>02+109</t>
@@ -3295,6 +3434,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5.099012, -73.718810</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>00+109</t>
@@ -3357,6 +3501,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5.098392, -73.714537</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>01+110</t>
@@ -3419,6 +3568,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5.096939, -73.708562</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
           <t>02+110</t>
@@ -3481,6 +3635,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5.100133, -73.718982</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>00+110</t>
@@ -3543,6 +3702,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5.099825, -73.714211</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>01+111</t>
@@ -3605,6 +3769,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5.098396, -73.709092</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>02+111</t>
@@ -3667,6 +3836,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5.098996, -73.718701</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>00+111</t>
@@ -3695,8 +3869,10 @@
           <t>Obsolescencia</t>
         </is>
       </c>
-      <c r="S35" t="b">
-        <v>0</v>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -3735,6 +3911,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5.092927, -73.676705</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
           <t>08+882</t>
@@ -3797,6 +3978,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5.090506, -73.665005</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>11+419</t>
@@ -3859,6 +4045,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5.086756, -73.651640</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>13+957</t>
@@ -3921,6 +4112,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5.084941, -73.640275</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>16+494</t>
@@ -3983,6 +4179,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5.082439, -73.629194</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>19+032</t>
@@ -4045,6 +4246,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5.080248, -73.615786</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
           <t>21+570</t>
@@ -4107,6 +4313,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5.075745, -73.603209</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>24+107</t>
@@ -4169,6 +4380,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5.066880, -73.588118</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>26+645</t>
@@ -4231,6 +4447,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5.058209, -73.572259</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>29+182</t>
@@ -4293,6 +4514,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5.049921, -73.556272</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
           <t>31+720</t>
@@ -4355,6 +4581,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5.039679, -73.541264</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>34+258</t>
@@ -4417,6 +4648,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5.031868, -73.523892</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>36+795</t>
@@ -4479,6 +4715,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5.021278, -73.509844</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>39+333</t>
@@ -4541,6 +4782,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5.013858, -73.494141</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
           <t>41+870</t>
@@ -4603,6 +4849,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5.004519, -73.477663</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>44+408</t>
@@ -4665,6 +4916,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4.993345, -73.458465</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
           <t>46+945</t>
@@ -4727,6 +4983,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4.976715, -73.435126</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>49+483</t>
@@ -4789,6 +5050,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4.961335, -73.412647</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
           <t>52+021</t>
@@ -4851,6 +5117,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4.945379, -73.388828</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
           <t>54+558</t>
@@ -4913,6 +5184,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4.930718, -73.365589</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
           <t>57+096</t>
@@ -4975,6 +5251,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>4.914135, -73.341542</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>59+633</t>
@@ -5037,6 +5318,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4.900435, -73.318651</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr">
         <is>
           <t>62+171</t>
@@ -5099,6 +5385,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4.884986, -73.294760</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
           <t>64+709</t>
@@ -5161,6 +5452,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4.868153, -73.272270</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
           <t>67+246</t>
@@ -5223,6 +5519,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4.858630, -73.254834</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
           <t>69+784</t>
@@ -5285,6 +5586,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4.854329, -73.244220</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
           <t>72+321</t>
@@ -5347,6 +5653,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4.850251, -73.234470</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
           <t>74+859</t>
@@ -5409,6 +5720,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4.843826, -73.224640</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
           <t>77+397</t>
@@ -5471,6 +5787,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>4.839897, -73.215681</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr">
         <is>
           <t>79+934</t>
@@ -5533,6 +5854,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4.836139, -73.204253</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>82+472</t>
@@ -5595,6 +5921,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4.831243, -73.195884</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>85+009</t>
@@ -5657,6 +5988,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4.826242, -73.184241</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr">
         <is>
           <t>87+547</t>
@@ -5719,6 +6055,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>4.821249, -73.174367</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>90+085</t>
@@ -5781,6 +6122,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>4.819494, -73.161425</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr">
         <is>
           <t>92+622</t>
@@ -5843,6 +6189,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>4.816410, -73.144824</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
           <t>95+160</t>
@@ -5905,6 +6256,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>4.812958, -73.128383</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr">
         <is>
           <t>97+697</t>
@@ -5967,6 +6323,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>4.809521, -73.112871</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>100+235</t>
@@ -6029,6 +6390,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4.808453, -73.095380</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr">
         <is>
           <t>102+773</t>
@@ -6091,6 +6457,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>4.806003, -73.078398</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr">
         <is>
           <t>105+310</t>
@@ -6153,6 +6524,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4.802906, -73.061710</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>107+848</t>
@@ -6215,6 +6591,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4.800006, -73.045033</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr">
         <is>
           <t>110+385</t>
@@ -6277,6 +6658,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4.795948, -73.028485</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr">
         <is>
           <t>112+923</t>
@@ -6339,6 +6725,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4.793477, -73.014666</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr">
         <is>
           <t>115+460</t>
@@ -6401,6 +6792,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4.793476, -73.001262</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr">
         <is>
           <t>117+998</t>
@@ -6463,6 +6859,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4.791386, -72.987869</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr">
         <is>
           <t>120+536</t>
@@ -6525,6 +6926,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>4.790258, -72.973633</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr">
         <is>
           <t>123+073</t>
@@ -6587,6 +6993,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4.788533, -72.961560</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr">
         <is>
           <t>125+611</t>
@@ -6649,6 +7060,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4.785941, -72.948128</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr">
         <is>
           <t>128+148</t>
@@ -6711,6 +7127,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4.783522, -72.933159</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr">
         <is>
           <t>130+686</t>
@@ -6773,6 +7194,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4.782976, -72.921340</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>133+224</t>
@@ -6835,6 +7261,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4.779752, -72.906656</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>135+761</t>
@@ -6897,6 +7328,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>5.080544, -73.610657</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr">
         <is>
           <t>22+557</t>
@@ -6959,6 +7395,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>5.061874, -73.580255</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>27+828</t>
@@ -7021,6 +7462,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>5.044243, -73.546355</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>33+098</t>
@@ -7083,6 +7529,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>5.026970, -73.514185</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>38+368</t>
@@ -7145,6 +7596,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>5.006616, -73.481745</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>43+639</t>
@@ -7207,6 +7663,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4.981716, -73.439785</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>48+909</t>
@@ -7269,6 +7730,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>4.948631, -73.391467</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>54+180</t>
@@ -7331,6 +7797,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>4.917091, -73.342883</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>59+450</t>
@@ -7393,6 +7864,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>4.884369, -73.294206</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>64+720</t>
@@ -7455,6 +7931,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>4.857410, -73.253388</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>69+991</t>
@@ -7517,6 +7998,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>4.849254, -73.232814</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>75+261</t>
@@ -7579,6 +8065,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4.838230, -73.212889</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>80+531</t>
@@ -7641,6 +8132,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4.830603, -73.193204</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>85+802</t>
@@ -7703,6 +8199,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>4.821617, -73.171068</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>91+072</t>
@@ -7765,6 +8266,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4.813822, -73.137286</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>96+343</t>
@@ -7827,6 +8333,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>4.807687, -73.104102</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>101+613</t>
@@ -7889,6 +8400,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>4.802469, -73.069858</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>106+883</t>
@@ -7951,6 +8467,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4.797817, -73.033983</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>112+154</t>
@@ -8013,6 +8534,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>4.792307, -73.004414</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>117+424</t>
@@ -8075,6 +8601,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4.788784, -72.976900</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>122+695</t>
@@ -8137,6 +8668,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4.786603, -72.947238</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr">
         <is>
           <t>127+965</t>
@@ -8199,6 +8735,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>4.781317, -72.921430</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr">
         <is>
           <t>133+235</t>
@@ -8261,6 +8802,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>5.098227, -73.711614</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>01+476</t>
@@ -8323,6 +8869,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4.970131, -73.427752</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr">
         <is>
           <t>50+452</t>
@@ -8385,6 +8936,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>4.894293, -73.311236</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr">
         <is>
           <t>62+909</t>
@@ -8447,6 +9003,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>4.849064, -73.233953</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>75+367</t>
@@ -8509,6 +9070,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>4.825256, -73.183126</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr">
         <is>
           <t>87+824</t>
@@ -8571,6 +9137,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4.809813, -73.112930</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>100+281</t>
@@ -8633,6 +9204,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>4.797461, -73.029417</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>112+738</t>
@@ -8695,6 +9271,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>4.788368, -72.963349</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>125+196</t>
@@ -8757,6 +9338,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>5.099492, -73.716022</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr">
         <is>
           <t>00+623</t>
@@ -8819,6 +9405,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>5.048380, -73.553594</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>32+094</t>
@@ -8881,6 +9472,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>5.022345, -73.509056</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>39+306</t>
@@ -8943,6 +9539,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>4.994673, -73.461546</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>46+518</t>
@@ -9005,6 +9606,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>4.950644, -73.396087</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>53+730</t>
@@ -9067,6 +9673,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>4.907871, -73.329255</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr">
         <is>
           <t>60+942</t>
@@ -9129,6 +9740,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4.863232, -73.263247</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr">
         <is>
           <t>68+154</t>
@@ -9191,6 +9807,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>4.849237, -73.233412</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr">
         <is>
           <t>75+367</t>
@@ -9253,6 +9874,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>4.835478, -73.203888</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>82+579</t>
@@ -9315,6 +9941,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4.821899, -73.176239</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>89+791</t>
@@ -9377,6 +10008,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>4.814289, -73.133908</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>97+003</t>
@@ -9439,6 +10075,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>4.805175, -73.086643</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr">
         <is>
           <t>104+215</t>
@@ -9501,6 +10142,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>4.799145, -73.038659</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr">
         <is>
           <t>111+427</t>
@@ -9563,6 +10209,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>4.790921, -72.997591</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>118+639</t>
@@ -9625,6 +10276,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>4.788546, -72.959559</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>125+851</t>
@@ -9687,6 +10343,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>4.783768, -72.921650</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>133+063</t>
@@ -9749,6 +10410,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>5.096740, -73.705619</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>03+245</t>
@@ -9811,6 +10477,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>4.818105, -73.154987</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>93+866</t>
@@ -9873,6 +10544,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>4.784783, -72.946747</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>128+123</t>
@@ -9935,6 +10611,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>4.828868, -73.193472</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>85+644</t>
@@ -9997,6 +10678,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>4.792283, -72.990735</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>119+901</t>
@@ -10059,6 +10745,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>4.791093, -72.991444</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>119+901</t>
@@ -10121,6 +10812,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>5.079488, -73.610083</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>22+610</t>
@@ -10183,6 +10879,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>4.931299, -73.367644</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>56+867</t>
@@ -10245,6 +10946,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>4.821062, -73.172460</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>91+125</t>
@@ -10307,6 +11013,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>4.786885, -72.962377</t>
+        </is>
+      </c>
       <c r="J142" t="inlineStr">
         <is>
           <t>125+382</t>
@@ -10369,6 +11080,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>5.093528, -73.686502</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>07+023</t>
@@ -10431,6 +11147,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>5.086597, -73.645147</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>15+587</t>
@@ -10493,6 +11214,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>5.075755, -73.601546</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>24+152</t>
@@ -10555,6 +11281,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>5.045715, -73.550152</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>32+716</t>
@@ -10617,6 +11348,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5.015617, -73.498387</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>41+280</t>
@@ -10679,6 +11415,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>4.975386, -73.432551</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>49+845</t>
@@ -10741,6 +11482,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>4.923226, -73.353346</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>58+409</t>
@@ -10803,6 +11549,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>4.869862, -73.273864</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>66+973</t>
@@ -10865,6 +11616,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>4.847242, -73.231787</t>
+        </is>
+      </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>75+538</t>
@@ -10927,6 +11683,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>4.832002, -73.199338</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>84+102</t>
@@ -10989,6 +11750,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>4.817657, -73.163172</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>92+667</t>
@@ -11051,6 +11817,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>4.809513, -73.104597</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>101+231</t>
@@ -11113,6 +11884,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>4.800563, -73.048515</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>109+795</t>
@@ -11175,6 +11951,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>4.791765, -72.998429</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>118+360</t>
@@ -11237,6 +12018,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>4.786261, -72.954591</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>126+924</t>
@@ -11299,6 +12085,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>4.781391, -72.908042</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr">
         <is>
           <t>135+488</t>
@@ -11361,6 +12152,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>5.081867, -73.618977</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr">
         <is>
           <t>21+240</t>
@@ -11423,6 +12219,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>4.939503, -73.379696</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr">
         <is>
           <t>55+497</t>
@@ -11485,6 +12286,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>4.823648, -73.177320</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
           <t>89+755</t>
@@ -11547,6 +12353,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>4.788489, -72.969294</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>124+012</t>
@@ -11609,6 +12420,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>5.093753, -73.680539</t>
+        </is>
+      </c>
       <c r="J163" t="inlineStr">
         <is>
           <t>08+299</t>
@@ -11671,6 +12487,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>5.091497, -73.676502</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>09+264</t>
@@ -11733,6 +12554,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>5.091257, -73.669794</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>10+229</t>
@@ -11795,6 +12621,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>5.090143, -73.665322</t>
+        </is>
+      </c>
       <c r="J166" t="inlineStr">
         <is>
           <t>11+194</t>
@@ -11857,6 +12688,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>5.088576, -73.660560</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
           <t>12+159</t>
@@ -11919,6 +12755,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>5.088811, -73.658097</t>
+        </is>
+      </c>
       <c r="J168" t="inlineStr">
         <is>
           <t>13+124</t>
@@ -11981,6 +12822,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>5.087707, -73.651818</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>14+089</t>
@@ -12043,6 +12889,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>5.085954, -73.646785</t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr">
         <is>
           <t>15+054</t>
@@ -12105,6 +12956,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>5.085646, -73.642073</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr">
         <is>
           <t>16+019</t>
@@ -12167,6 +13023,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>5.084272, -73.638136</t>
+        </is>
+      </c>
       <c r="J172" t="inlineStr">
         <is>
           <t>16+984</t>
@@ -12229,6 +13090,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>5.083438, -73.633252</t>
+        </is>
+      </c>
       <c r="J173" t="inlineStr">
         <is>
           <t>17+949</t>
@@ -12291,6 +13157,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>5.084070, -73.629558</t>
+        </is>
+      </c>
       <c r="J174" t="inlineStr">
         <is>
           <t>18+914</t>
@@ -12353,6 +13224,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>5.081534, -73.625574</t>
+        </is>
+      </c>
       <c r="J175" t="inlineStr">
         <is>
           <t>19+879</t>
@@ -12415,6 +13291,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>5.081883, -73.619729</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr">
         <is>
           <t>20+844</t>
@@ -12477,6 +13358,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>5.080573, -73.615246</t>
+        </is>
+      </c>
       <c r="J177" t="inlineStr">
         <is>
           <t>21+809</t>
@@ -12539,6 +13425,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>5.080711, -73.610712</t>
+        </is>
+      </c>
       <c r="J178" t="inlineStr">
         <is>
           <t>22+774</t>
@@ -12601,6 +13492,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>5.077374, -73.603751</t>
+        </is>
+      </c>
       <c r="J179" t="inlineStr">
         <is>
           <t>23+739</t>
@@ -12663,6 +13559,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>5.074542, -73.599798</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>24+704</t>
@@ -12725,6 +13626,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>5.071368, -73.592508</t>
+        </is>
+      </c>
       <c r="J181" t="inlineStr">
         <is>
           <t>25+669</t>
@@ -12787,6 +13693,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>5.066751, -73.586495</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>26+634</t>
@@ -12849,6 +13760,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>5.064049, -73.582272</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr">
         <is>
           <t>27+599</t>
@@ -12911,6 +13827,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>5.059516, -73.575131</t>
+        </is>
+      </c>
       <c r="J184" t="inlineStr">
         <is>
           <t>28+564</t>
@@ -12973,6 +13894,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>5.056305, -73.568579</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr">
         <is>
           <t>29+529</t>
@@ -13035,6 +13961,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>5.054166, -73.563184</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>30+494</t>
@@ -13097,6 +14028,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>5.051133, -73.556723</t>
+        </is>
+      </c>
       <c r="J187" t="inlineStr">
         <is>
           <t>31+459</t>
@@ -13159,6 +14095,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>5.045719, -73.552698</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>32+424</t>
@@ -13221,6 +14162,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>5.043894, -73.544973</t>
+        </is>
+      </c>
       <c r="J189" t="inlineStr">
         <is>
           <t>33+389</t>
@@ -13283,6 +14229,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>5.041061, -73.540633</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr">
         <is>
           <t>34+354</t>
@@ -13345,6 +14296,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>5.036665, -73.534570</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr">
         <is>
           <t>35+319</t>
@@ -13407,6 +14363,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>5.032783, -73.527837</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>36+284</t>
@@ -13469,6 +14430,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>5.029241, -73.522945</t>
+        </is>
+      </c>
       <c r="J193" t="inlineStr">
         <is>
           <t>37+249</t>
@@ -13531,6 +14497,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>5.027429, -73.516804</t>
+        </is>
+      </c>
       <c r="J194" t="inlineStr">
         <is>
           <t>38+214</t>
@@ -13593,6 +14564,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>5.023561, -73.510230</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr">
         <is>
           <t>39+179</t>
@@ -13655,6 +14631,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>5.019144, -73.504404</t>
+        </is>
+      </c>
       <c r="J196" t="inlineStr">
         <is>
           <t>40+144</t>
@@ -13717,6 +14698,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>5.017196, -73.499517</t>
+        </is>
+      </c>
       <c r="J197" t="inlineStr">
         <is>
           <t>41+109</t>
@@ -13779,6 +14765,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>5.013871, -73.491696</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
           <t>42+074</t>
@@ -13841,6 +14832,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>5.010207, -73.487219</t>
+        </is>
+      </c>
       <c r="J199" t="inlineStr">
         <is>
           <t>43+039</t>
@@ -13903,6 +14899,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>5.005081, -73.481009</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr">
         <is>
           <t>44+004</t>
@@ -13965,6 +14966,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>5.002592, -73.473497</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr">
         <is>
           <t>44+969</t>
@@ -14027,6 +15033,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>4.997589, -73.468057</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr">
         <is>
           <t>45+934</t>
@@ -14089,6 +15100,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>4.992010, -73.458989</t>
+        </is>
+      </c>
       <c r="J203" t="inlineStr">
         <is>
           <t>46+899</t>
@@ -14151,6 +15167,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>4.986602, -73.450900</t>
+        </is>
+      </c>
       <c r="J204" t="inlineStr">
         <is>
           <t>47+864</t>
@@ -14213,6 +15234,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>4.980692, -73.440745</t>
+        </is>
+      </c>
       <c r="J205" t="inlineStr">
         <is>
           <t>48+829</t>
@@ -14275,6 +15301,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>4.974586, -73.433509</t>
+        </is>
+      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>49+794</t>
@@ -14337,6 +15368,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>4.968110, -73.424995</t>
+        </is>
+      </c>
       <c r="J207" t="inlineStr">
         <is>
           <t>50+759</t>
@@ -14399,6 +15435,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>4.964039, -73.414489</t>
+        </is>
+      </c>
       <c r="J208" t="inlineStr">
         <is>
           <t>51+724</t>
@@ -14461,6 +15502,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>4.957538, -73.405937</t>
+        </is>
+      </c>
       <c r="J209" t="inlineStr">
         <is>
           <t>52+689</t>
@@ -14523,6 +15569,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>4.951375, -73.397727</t>
+        </is>
+      </c>
       <c r="J210" t="inlineStr">
         <is>
           <t>53+654</t>
@@ -14585,6 +15636,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>4.945903, -73.389478</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
           <t>54+619</t>
@@ -14647,6 +15703,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>4.940168, -73.378332</t>
+        </is>
+      </c>
       <c r="J212" t="inlineStr">
         <is>
           <t>55+584</t>
@@ -14709,6 +15770,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>4.932947, -73.370554</t>
+        </is>
+      </c>
       <c r="J213" t="inlineStr">
         <is>
           <t>56+549</t>
@@ -14771,6 +15837,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>4.928402, -73.362255</t>
+        </is>
+      </c>
       <c r="J214" t="inlineStr">
         <is>
           <t>57+514</t>
@@ -14833,6 +15904,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>4.921968, -73.351969</t>
+        </is>
+      </c>
       <c r="J215" t="inlineStr">
         <is>
           <t>58+479</t>
@@ -14895,6 +15971,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>4.916537, -73.344568</t>
+        </is>
+      </c>
       <c r="J216" t="inlineStr">
         <is>
           <t>59+444</t>
@@ -14957,6 +16038,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>4.909206, -73.334715</t>
+        </is>
+      </c>
       <c r="J217" t="inlineStr">
         <is>
           <t>60+409</t>
@@ -15019,6 +16105,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>4.903466, -73.326066</t>
+        </is>
+      </c>
       <c r="J218" t="inlineStr">
         <is>
           <t>61+374</t>
@@ -15081,6 +16172,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>4.898116, -73.317592</t>
+        </is>
+      </c>
       <c r="J219" t="inlineStr">
         <is>
           <t>62+339</t>
@@ -15143,6 +16239,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>4.891964, -73.308767</t>
+        </is>
+      </c>
       <c r="J220" t="inlineStr">
         <is>
           <t>63+304</t>
@@ -15205,6 +16306,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>4.887082, -73.299373</t>
+        </is>
+      </c>
       <c r="J221" t="inlineStr">
         <is>
           <t>64+269</t>
@@ -15267,6 +16373,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>4.880678, -73.291990</t>
+        </is>
+      </c>
       <c r="J222" t="inlineStr">
         <is>
           <t>65+234</t>
@@ -15329,6 +16440,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>4.873596, -73.282368</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr">
         <is>
           <t>66+199</t>
@@ -15391,6 +16507,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>4.868118, -73.273213</t>
+        </is>
+      </c>
       <c r="J224" t="inlineStr">
         <is>
           <t>67+164</t>
@@ -15453,6 +16574,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>4.861718, -73.264356</t>
+        </is>
+      </c>
       <c r="J225" t="inlineStr">
         <is>
           <t>68+129</t>
@@ -15515,6 +16641,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>4.857826, -73.257235</t>
+        </is>
+      </c>
       <c r="J226" t="inlineStr">
         <is>
           <t>69+094</t>
@@ -15577,6 +16708,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>4.858235, -73.252990</t>
+        </is>
+      </c>
       <c r="J227" t="inlineStr">
         <is>
           <t>70+059</t>
@@ -15639,6 +16775,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>4.854468, -73.251190</t>
+        </is>
+      </c>
       <c r="J228" t="inlineStr">
         <is>
           <t>71+024</t>
@@ -15701,6 +16842,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>4.853966, -73.247195</t>
+        </is>
+      </c>
       <c r="J229" t="inlineStr">
         <is>
           <t>71+989</t>
@@ -15763,6 +16909,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>4.851685, -73.242309</t>
+        </is>
+      </c>
       <c r="J230" t="inlineStr">
         <is>
           <t>72+954</t>
@@ -15825,6 +16976,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>4.850639, -73.239843</t>
+        </is>
+      </c>
       <c r="J231" t="inlineStr">
         <is>
           <t>73+919</t>
@@ -15887,6 +17043,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>4.847832, -73.234045</t>
+        </is>
+      </c>
       <c r="J232" t="inlineStr">
         <is>
           <t>74+884</t>
@@ -15949,6 +17110,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>4.846505, -73.230882</t>
+        </is>
+      </c>
       <c r="J233" t="inlineStr">
         <is>
           <t>75+849</t>
@@ -16011,6 +17177,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>4.844394, -73.228100</t>
+        </is>
+      </c>
       <c r="J234" t="inlineStr">
         <is>
           <t>76+814</t>
@@ -16073,6 +17244,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>4.843224, -73.224254</t>
+        </is>
+      </c>
       <c r="J235" t="inlineStr">
         <is>
           <t>77+779</t>
@@ -16135,6 +17311,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>4.841719, -73.220515</t>
+        </is>
+      </c>
       <c r="J236" t="inlineStr">
         <is>
           <t>78+744</t>
@@ -16197,6 +17378,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>4.839530, -73.216500</t>
+        </is>
+      </c>
       <c r="J237" t="inlineStr">
         <is>
           <t>79+709</t>
@@ -16259,6 +17445,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>4.838342, -73.211539</t>
+        </is>
+      </c>
       <c r="J238" t="inlineStr">
         <is>
           <t>80+674</t>
@@ -16321,6 +17512,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>4.837871, -73.208688</t>
+        </is>
+      </c>
       <c r="J239" t="inlineStr">
         <is>
           <t>81+639</t>
@@ -16383,6 +17579,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>4.836044, -73.205456</t>
+        </is>
+      </c>
       <c r="J240" t="inlineStr">
         <is>
           <t>82+604</t>
@@ -16445,6 +17646,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>4.834927, -73.199740</t>
+        </is>
+      </c>
       <c r="J241" t="inlineStr">
         <is>
           <t>83+569</t>
@@ -16507,6 +17713,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>4.833177, -73.198483</t>
+        </is>
+      </c>
       <c r="J242" t="inlineStr">
         <is>
           <t>84+534</t>
@@ -16569,6 +17780,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>4.830427, -73.194307</t>
+        </is>
+      </c>
       <c r="J243" t="inlineStr">
         <is>
           <t>85+499</t>
@@ -16631,6 +17847,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>4.828643, -73.190086</t>
+        </is>
+      </c>
       <c r="J244" t="inlineStr">
         <is>
           <t>86+464</t>
@@ -16693,6 +17914,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>4.827290, -73.186183</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>87+429</t>
@@ -16755,6 +17981,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>4.825318, -73.183030</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>88+394</t>
@@ -16817,6 +18048,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>4.824762, -73.178691</t>
+        </is>
+      </c>
       <c r="J247" t="inlineStr">
         <is>
           <t>89+359</t>
@@ -16879,6 +18115,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>4.823138, -73.175198</t>
+        </is>
+      </c>
       <c r="J248" t="inlineStr">
         <is>
           <t>90+324</t>
@@ -16941,6 +18182,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>4.821465, -73.171454</t>
+        </is>
+      </c>
       <c r="J249" t="inlineStr">
         <is>
           <t>91+289</t>
@@ -17003,6 +18249,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>4.818788, -73.165652</t>
+        </is>
+      </c>
       <c r="J250" t="inlineStr">
         <is>
           <t>92+254</t>
@@ -17065,6 +18316,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>4.818723, -73.158116</t>
+        </is>
+      </c>
       <c r="J251" t="inlineStr">
         <is>
           <t>93+219</t>
@@ -17127,6 +18383,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>4.817237, -73.151030</t>
+        </is>
+      </c>
       <c r="J252" t="inlineStr">
         <is>
           <t>94+184</t>
@@ -17189,6 +18450,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>4.814824, -73.145413</t>
+        </is>
+      </c>
       <c r="J253" t="inlineStr">
         <is>
           <t>95+149</t>
@@ -17251,6 +18517,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>4.816059, -73.138667</t>
+        </is>
+      </c>
       <c r="J254" t="inlineStr">
         <is>
           <t>96+114</t>
@@ -17313,6 +18584,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>4.813962, -73.133997</t>
+        </is>
+      </c>
       <c r="J255" t="inlineStr">
         <is>
           <t>97+079</t>
@@ -17375,6 +18651,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>4.812869, -73.126147</t>
+        </is>
+      </c>
       <c r="J256" t="inlineStr">
         <is>
           <t>98+044</t>
@@ -17437,6 +18718,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>4.811200, -73.119431</t>
+        </is>
+      </c>
       <c r="J257" t="inlineStr">
         <is>
           <t>99+009</t>
@@ -17499,6 +18785,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>4.809474, -73.115175</t>
+        </is>
+      </c>
       <c r="J258" t="inlineStr">
         <is>
           <t>99+974</t>
@@ -17561,6 +18852,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>4.808516, -73.107270</t>
+        </is>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
           <t>100+939</t>
@@ -17623,6 +18919,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>4.808447, -73.102505</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr">
         <is>
           <t>101+904</t>
@@ -17685,6 +18986,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>4.808119, -73.095930</t>
+        </is>
+      </c>
       <c r="J261" t="inlineStr">
         <is>
           <t>102+869</t>
@@ -17747,6 +19053,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>4.807352, -73.088771</t>
+        </is>
+      </c>
       <c r="J262" t="inlineStr">
         <is>
           <t>103+834</t>
@@ -17809,6 +19120,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>4.806469, -73.082282</t>
+        </is>
+      </c>
       <c r="J263" t="inlineStr">
         <is>
           <t>104+799</t>
@@ -17871,6 +19187,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>4.804998, -73.076065</t>
+        </is>
+      </c>
       <c r="J264" t="inlineStr">
         <is>
           <t>105+764</t>
@@ -17933,6 +19254,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>4.803897, -73.070242</t>
+        </is>
+      </c>
       <c r="J265" t="inlineStr">
         <is>
           <t>106+729</t>
@@ -17995,6 +19321,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>4.802497, -73.064557</t>
+        </is>
+      </c>
       <c r="J266" t="inlineStr">
         <is>
           <t>107+694</t>
@@ -18057,6 +19388,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>4.800479, -73.057772</t>
+        </is>
+      </c>
       <c r="J267" t="inlineStr">
         <is>
           <t>108+659</t>
@@ -18119,6 +19455,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>4.799140, -73.051284</t>
+        </is>
+      </c>
       <c r="J268" t="inlineStr">
         <is>
           <t>109+624</t>
@@ -18181,6 +19522,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>4.799185, -73.045306</t>
+        </is>
+      </c>
       <c r="J269" t="inlineStr">
         <is>
           <t>110+589</t>
@@ -18243,6 +19589,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>4.797424, -73.037316</t>
+        </is>
+      </c>
       <c r="J270" t="inlineStr">
         <is>
           <t>111+554</t>
@@ -18305,6 +19656,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>4.796308, -73.031389</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr">
         <is>
           <t>112+519</t>
@@ -18367,6 +19723,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>4.795049, -73.026316</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr">
         <is>
           <t>113+484</t>
@@ -18429,6 +19790,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>4.795300, -73.020310</t>
+        </is>
+      </c>
       <c r="J273" t="inlineStr">
         <is>
           <t>114+449</t>
@@ -18491,6 +19857,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>4.795260, -73.013602</t>
+        </is>
+      </c>
       <c r="J274" t="inlineStr">
         <is>
           <t>115+414</t>
@@ -18553,6 +19924,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>4.794079, -73.010288</t>
+        </is>
+      </c>
       <c r="J275" t="inlineStr">
         <is>
           <t>116+379</t>
@@ -18615,6 +19991,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>4.793456, -73.003929</t>
+        </is>
+      </c>
       <c r="J276" t="inlineStr">
         <is>
           <t>117+344</t>
@@ -18677,6 +20058,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>4.792276, -72.998079</t>
+        </is>
+      </c>
       <c r="J277" t="inlineStr">
         <is>
           <t>118+309</t>
@@ -18739,6 +20125,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>4.792773, -72.992753</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr">
         <is>
           <t>119+274</t>
@@ -18801,6 +20192,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>4.790145, -72.988311</t>
+        </is>
+      </c>
       <c r="J279" t="inlineStr">
         <is>
           <t>120+239</t>
@@ -18863,6 +20259,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>4.789771, -72.983566</t>
+        </is>
+      </c>
       <c r="J280" t="inlineStr">
         <is>
           <t>121+204</t>
@@ -18925,6 +20326,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>4.788684, -72.978351</t>
+        </is>
+      </c>
       <c r="J281" t="inlineStr">
         <is>
           <t>122+169</t>
@@ -18987,6 +20393,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>4.788790, -72.974834</t>
+        </is>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
           <t>123+134</t>
@@ -19049,6 +20460,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>4.787277, -72.969306</t>
+        </is>
+      </c>
       <c r="J283" t="inlineStr">
         <is>
           <t>124+099</t>
@@ -19111,6 +20527,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>4.788268, -72.963916</t>
+        </is>
+      </c>
       <c r="J284" t="inlineStr">
         <is>
           <t>125+064</t>
@@ -19173,6 +20594,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>4.786875, -72.958072</t>
+        </is>
+      </c>
       <c r="J285" t="inlineStr">
         <is>
           <t>126+029</t>
@@ -19235,6 +20661,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>4.787859, -72.954413</t>
+        </is>
+      </c>
       <c r="J286" t="inlineStr">
         <is>
           <t>126+994</t>
@@ -19297,6 +20728,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>4.785880, -72.947182</t>
+        </is>
+      </c>
       <c r="J287" t="inlineStr">
         <is>
           <t>127+959</t>
@@ -19359,6 +20795,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>4.784865, -72.942196</t>
+        </is>
+      </c>
       <c r="J288" t="inlineStr">
         <is>
           <t>128+924</t>
@@ -19421,6 +20862,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>4.784742, -72.939446</t>
+        </is>
+      </c>
       <c r="J289" t="inlineStr">
         <is>
           <t>129+889</t>
@@ -19483,6 +20929,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>4.784752, -72.934130</t>
+        </is>
+      </c>
       <c r="J290" t="inlineStr">
         <is>
           <t>130+854</t>
@@ -19545,6 +20996,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>4.784643, -72.928418</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr">
         <is>
           <t>131+819</t>
@@ -19607,6 +21063,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>4.782067, -72.922848</t>
+        </is>
+      </c>
       <c r="J292" t="inlineStr">
         <is>
           <t>132+784</t>
@@ -19669,6 +21130,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>4.783542, -72.918384</t>
+        </is>
+      </c>
       <c r="J293" t="inlineStr">
         <is>
           <t>133+749</t>
@@ -19731,6 +21197,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>4.782147, -72.913307</t>
+        </is>
+      </c>
       <c r="J294" t="inlineStr">
         <is>
           <t>134+714</t>
@@ -19793,6 +21264,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>4.780339, -72.907927</t>
+        </is>
+      </c>
       <c r="J295" t="inlineStr">
         <is>
           <t>135+679</t>
@@ -19855,6 +21331,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>4.781075, -72.901535</t>
+        </is>
+      </c>
       <c r="J296" t="inlineStr">
         <is>
           <t>136+644</t>
@@ -19917,6 +21398,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>5.099284, -73.718054</t>
+        </is>
+      </c>
       <c r="J297" t="inlineStr">
         <is>
           <t>00+579</t>
@@ -19979,6 +21465,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>5.098186, -73.713811</t>
+        </is>
+      </c>
       <c r="J298" t="inlineStr">
         <is>
           <t>01+544</t>
@@ -20041,6 +21532,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>5.096628, -73.709121</t>
+        </is>
+      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>02+509</t>
@@ -20103,6 +21599,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>5.096106, -73.702339</t>
+        </is>
+      </c>
       <c r="J300" t="inlineStr">
         <is>
           <t>03+474</t>
@@ -20165,6 +21666,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>5.095904, -73.697801</t>
+        </is>
+      </c>
       <c r="J301" t="inlineStr">
         <is>
           <t>04+439</t>
@@ -20227,6 +21733,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>5.095023, -73.694719</t>
+        </is>
+      </c>
       <c r="J302" t="inlineStr">
         <is>
           <t>05+404</t>
@@ -20289,6 +21800,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>5.094628, -73.688392</t>
+        </is>
+      </c>
       <c r="J303" t="inlineStr">
         <is>
           <t>06+369</t>
@@ -20351,6 +21867,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>5.088965, -73.666249</t>
+        </is>
+      </c>
       <c r="J304" t="inlineStr">
         <is>
           <t>11+191</t>
@@ -20413,6 +21934,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>5.080831, -73.611856</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr">
         <is>
           <t>22+610</t>
@@ -20475,6 +22001,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>5.040207, -73.540333</t>
+        </is>
+      </c>
       <c r="J306" t="inlineStr">
         <is>
           <t>34+029</t>
@@ -20537,6 +22068,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>5.002156, -73.470736</t>
+        </is>
+      </c>
       <c r="J307" t="inlineStr">
         <is>
           <t>45+448</t>
@@ -20599,6 +22135,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>4.931454, -73.367658</t>
+        </is>
+      </c>
       <c r="J308" t="inlineStr">
         <is>
           <t>56+867</t>
@@ -20661,6 +22202,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>4.862077, -73.262547</t>
+        </is>
+      </c>
       <c r="J309" t="inlineStr">
         <is>
           <t>68+287</t>
@@ -20723,6 +22269,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>4.840101, -73.215535</t>
+        </is>
+      </c>
       <c r="J310" t="inlineStr">
         <is>
           <t>79+706</t>
@@ -20785,6 +22336,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>4.821801, -73.171905</t>
+        </is>
+      </c>
       <c r="J311" t="inlineStr">
         <is>
           <t>91+125</t>
@@ -20847,6 +22403,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>4.806641, -73.096075</t>
+        </is>
+      </c>
       <c r="J312" t="inlineStr">
         <is>
           <t>102+544</t>
@@ -20909,6 +22470,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>4.795782, -73.023270</t>
+        </is>
+      </c>
       <c r="J313" t="inlineStr">
         <is>
           <t>113+963</t>
@@ -20971,6 +22537,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>4.787603, -72.960936</t>
+        </is>
+      </c>
       <c r="J314" t="inlineStr">
         <is>
           <t>125+382</t>
@@ -21033,6 +22604,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>4.780226, -72.900922</t>
+        </is>
+      </c>
       <c r="J315" t="inlineStr">
         <is>
           <t>136+802</t>
@@ -21095,6 +22671,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>5.088044, -73.653743</t>
+        </is>
+      </c>
       <c r="J316" t="inlineStr">
         <is>
           <t>13+931</t>
@@ -21157,6 +22738,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>5.072187, -73.594721</t>
+        </is>
+      </c>
       <c r="J317" t="inlineStr">
         <is>
           <t>25+351</t>
@@ -21219,6 +22805,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>5.030939, -73.524093</t>
+        </is>
+      </c>
       <c r="J318" t="inlineStr">
         <is>
           <t>36+770</t>
@@ -21281,6 +22872,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>4.984415, -73.447455</t>
+        </is>
+      </c>
       <c r="J319" t="inlineStr">
         <is>
           <t>48+189</t>
@@ -21343,6 +22939,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>4.914429, -73.342555</t>
+        </is>
+      </c>
       <c r="J320" t="inlineStr">
         <is>
           <t>59+608</t>
@@ -21405,6 +23006,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>4.856220, -73.251323</t>
+        </is>
+      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>71+027</t>
@@ -21467,6 +23073,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>4.836232, -73.204582</t>
+        </is>
+      </c>
       <c r="J322" t="inlineStr">
         <is>
           <t>82+446</t>
@@ -21529,6 +23140,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>4.817154, -73.153583</t>
+        </is>
+      </c>
       <c r="J323" t="inlineStr">
         <is>
           <t>93+866</t>
@@ -21591,6 +23207,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>4.804429, -73.078608</t>
+        </is>
+      </c>
       <c r="J324" t="inlineStr">
         <is>
           <t>105+285</t>
@@ -21653,6 +23274,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>4.794600, -73.007761</t>
+        </is>
+      </c>
       <c r="J325" t="inlineStr">
         <is>
           <t>116+704</t>
@@ -21715,6 +23341,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>4.786602, -72.947202</t>
+        </is>
+      </c>
       <c r="J326" t="inlineStr">
         <is>
           <t>128+123</t>
@@ -21777,6 +23408,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>5.098380, -73.708916</t>
+        </is>
+      </c>
       <c r="J327" t="inlineStr">
         <is>
           <t>02+512</t>
@@ -21839,6 +23475,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>5.033118, -73.528278</t>
+        </is>
+      </c>
       <c r="J328" t="inlineStr">
         <is>
           <t>36+215</t>
@@ -21901,6 +23542,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>4.937208, -73.376936</t>
+        </is>
+      </c>
       <c r="J329" t="inlineStr">
         <is>
           <t>55+791</t>
@@ -21963,6 +23609,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>4.848106, -73.234468</t>
+        </is>
+      </c>
       <c r="J330" t="inlineStr">
         <is>
           <t>75+367</t>
@@ -22025,6 +23676,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>4.816092, -73.146151</t>
+        </is>
+      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>94+942</t>
@@ -22087,6 +23743,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>4.795334, -73.018882</t>
+        </is>
+      </c>
       <c r="J332" t="inlineStr">
         <is>
           <t>114+518</t>
@@ -22149,6 +23810,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>4.780732, -72.915808</t>
+        </is>
+      </c>
       <c r="J333" t="inlineStr">
         <is>
           <t>134+094</t>
@@ -22211,6 +23877,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>5.034952, -73.532113</t>
+        </is>
+      </c>
       <c r="J334" t="inlineStr">
         <is>
           <t>35+628</t>
@@ -22273,6 +23944,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>4.805087, -73.086017</t>
+        </is>
+      </c>
       <c r="J335" t="inlineStr">
         <is>
           <t>104+143</t>
@@ -22335,6 +24011,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>5.022225, -73.506514</t>
+        </is>
+      </c>
       <c r="J336" t="inlineStr">
         <is>
           <t>39+739</t>
@@ -22397,6 +24078,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>4.802174, -73.058573</t>
+        </is>
+      </c>
       <c r="J337" t="inlineStr">
         <is>
           <t>108+254</t>
@@ -22459,6 +24145,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>5.094999, -73.689684</t>
+        </is>
+      </c>
       <c r="J338" t="inlineStr">
         <is>
           <t>06+473</t>
@@ -22516,6 +24207,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>5.089935, -73.666205</t>
+        </is>
+      </c>
       <c r="J339" t="inlineStr">
         <is>
           <t>11+199</t>
@@ -22573,6 +24269,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>5.085077, -73.644207</t>
+        </is>
+      </c>
       <c r="J340" t="inlineStr">
         <is>
           <t>15+924</t>
@@ -22630,6 +24331,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>5.082533, -73.621266</t>
+        </is>
+      </c>
       <c r="J341" t="inlineStr">
         <is>
           <t>20+649</t>
@@ -22687,6 +24393,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>5.070887, -73.594123</t>
+        </is>
+      </c>
       <c r="J342" t="inlineStr">
         <is>
           <t>25+374</t>
@@ -22744,6 +24455,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>5.053590, -73.564555</t>
+        </is>
+      </c>
       <c r="J343" t="inlineStr">
         <is>
           <t>30+099</t>
@@ -22801,6 +24517,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>5.038455, -73.537450</t>
+        </is>
+      </c>
       <c r="J344" t="inlineStr">
         <is>
           <t>34+825</t>
@@ -22858,6 +24579,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>5.022781, -73.509029</t>
+        </is>
+      </c>
       <c r="J345" t="inlineStr">
         <is>
           <t>39+550</t>
@@ -22915,6 +24641,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>5.006305, -73.478887</t>
+        </is>
+      </c>
       <c r="J346" t="inlineStr">
         <is>
           <t>44+275</t>
@@ -22972,6 +24703,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>4.980943, -73.440248</t>
+        </is>
+      </c>
       <c r="J347" t="inlineStr">
         <is>
           <t>49+000</t>
@@ -23029,6 +24765,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>4.951915, -73.396590</t>
+        </is>
+      </c>
       <c r="J348" t="inlineStr">
         <is>
           <t>53+725</t>
@@ -23086,6 +24827,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>4.921878, -73.352737</t>
+        </is>
+      </c>
       <c r="J349" t="inlineStr">
         <is>
           <t>58+450</t>
@@ -23143,6 +24889,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>4.894275, -73.310456</t>
+        </is>
+      </c>
       <c r="J350" t="inlineStr">
         <is>
           <t>63+176</t>
@@ -23200,6 +24951,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>4.863728, -73.267565</t>
+        </is>
+      </c>
       <c r="J351" t="inlineStr">
         <is>
           <t>67+901</t>
@@ -23257,6 +25013,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>4.852272, -73.243347</t>
+        </is>
+      </c>
       <c r="J352" t="inlineStr">
         <is>
           <t>72+626</t>
@@ -23314,6 +25075,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>4.843715, -73.225231</t>
+        </is>
+      </c>
       <c r="J353" t="inlineStr">
         <is>
           <t>77+351</t>
@@ -23371,6 +25137,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>4.836279, -73.207558</t>
+        </is>
+      </c>
       <c r="J354" t="inlineStr">
         <is>
           <t>82+076</t>
@@ -23428,6 +25199,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>4.828267, -73.189316</t>
+        </is>
+      </c>
       <c r="J355" t="inlineStr">
         <is>
           <t>86+801</t>
@@ -23485,6 +25261,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>4.820541, -73.170402</t>
+        </is>
+      </c>
       <c r="J356" t="inlineStr">
         <is>
           <t>91+527</t>
@@ -23542,6 +25323,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>4.815518, -73.137912</t>
+        </is>
+      </c>
       <c r="J357" t="inlineStr">
         <is>
           <t>96+252</t>
@@ -23599,6 +25385,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>4.809095, -73.108306</t>
+        </is>
+      </c>
       <c r="J358" t="inlineStr">
         <is>
           <t>100+977</t>
@@ -23656,6 +25447,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>4.804402, -73.077016</t>
+        </is>
+      </c>
       <c r="J359" t="inlineStr">
         <is>
           <t>105+702</t>
@@ -23713,6 +25509,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>4.798653, -73.045692</t>
+        </is>
+      </c>
       <c r="J360" t="inlineStr">
         <is>
           <t>110+427</t>
@@ -23770,6 +25571,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>4.793866, -73.014772</t>
+        </is>
+      </c>
       <c r="J361" t="inlineStr">
         <is>
           <t>115+152</t>
@@ -23827,6 +25633,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>4.792155, -72.991293</t>
+        </is>
+      </c>
       <c r="J362" t="inlineStr">
         <is>
           <t>119+878</t>
@@ -23884,6 +25695,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>4.786991, -72.964825</t>
+        </is>
+      </c>
       <c r="J363" t="inlineStr">
         <is>
           <t>124+603</t>
@@ -23941,6 +25757,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>4.784431, -72.942220</t>
+        </is>
+      </c>
       <c r="J364" t="inlineStr">
         <is>
           <t>129+328</t>
@@ -23998,6 +25819,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>4.782902, -72.915751</t>
+        </is>
+      </c>
       <c r="J365" t="inlineStr">
         <is>
           <t>134+053</t>
@@ -24055,6 +25881,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>5.099435, -73.710844</t>
+        </is>
+      </c>
       <c r="J366" t="inlineStr">
         <is>
           <t>01+748</t>
@@ -24112,6 +25943,11 @@
           <t>AS</t>
         </is>
       </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>5.060237, -73.575706</t>
+        </is>
+      </c>
       <c r="J367" t="inlineStr">
         <is>
           <t>28+320</t>
@@ -24174,6 +26010,11 @@
           <t>SA</t>
         </is>
       </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>4.849715, -73.239299</t>
+        </is>
+      </c>
       <c r="J368" t="inlineStr">
         <is>
           <t>73+996</t>
@@ -24234,6 +26075,11 @@
       <c r="H369" t="inlineStr">
         <is>
           <t>AS</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>4.790377, -72.991306</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -26328,25 +28174,35 @@
           <t>TPR-02</t>
         </is>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>Seleccione el estado encontrado del activo.</t>
         </is>
       </c>
-      <c r="M2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>1</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -26378,25 +28234,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G3" t="b">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>Limpie completamente el poste.</t>
         </is>
       </c>
-      <c r="M3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -26428,25 +28294,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G4" t="b">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>Verifique ausencia de polvo y humedad.</t>
         </is>
       </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>1</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -26478,25 +28354,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Revise cable, carcasa y funcionamiento.</t>
         </is>
       </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -26528,25 +28414,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G6" t="b">
-        <v>1</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>Pruebe todas las teclas.</t>
         </is>
       </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>1</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -26578,25 +28474,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G7" t="b">
-        <v>1</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Realice llamada de prueba.</t>
         </is>
       </c>
-      <c r="M7" t="b">
-        <v>0</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -26628,8 +28534,10 @@
           <t>TPR-03</t>
         </is>
       </c>
-      <c r="G8" t="b">
-        <v>1</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="H8" t="n">
         <v>10</v>
@@ -26647,17 +28555,25 @@
           <t>Medir con multímetro.</t>
         </is>
       </c>
-      <c r="M8" t="b">
-        <v>0</v>
-      </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -26689,25 +28605,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G9" t="b">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>Limpiar superficie del panel.</t>
         </is>
       </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>1</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -26739,25 +28665,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G10" t="b">
-        <v>1</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>Verifique apertura y cierre.</t>
         </is>
       </c>
-      <c r="M10" t="b">
-        <v>0</v>
-      </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -26789,25 +28725,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G11" t="b">
-        <v>1</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>Abra y cierre la puerta para validar.</t>
         </is>
       </c>
-      <c r="M11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="b">
-        <v>0</v>
-      </c>
-      <c r="P11" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -26839,25 +28785,35 @@
           <t>TPR-01</t>
         </is>
       </c>
-      <c r="G12" t="b">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>Si responde Sí, describa la novedad.</t>
         </is>
       </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="b">
-        <v>0</v>
-      </c>
-      <c r="P12" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -26889,25 +28845,35 @@
           <t>TPR-05</t>
         </is>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>Describa hallazgos y recomendaciones.</t>
         </is>
       </c>
-      <c r="M13" t="b">
-        <v>0</v>
-      </c>
-      <c r="O13" t="b">
-        <v>0</v>
-      </c>
-      <c r="P13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -26939,25 +28905,35 @@
           <t>TPR-08</t>
         </is>
       </c>
-      <c r="G14" t="b">
-        <v>1</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Fotografía general del poste.</t>
         </is>
       </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-      <c r="O14" t="b">
-        <v>0</v>
-      </c>
-      <c r="P14" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -26989,25 +28965,35 @@
           <t>TPR-08</t>
         </is>
       </c>
-      <c r="G15" t="b">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>Fotografía con gabinete abierto.</t>
         </is>
       </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-      <c r="O15" t="b">
-        <v>0</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -27039,25 +29025,35 @@
           <t>TPR-08</t>
         </is>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>Solo si existen novedades.</t>
         </is>
       </c>
-      <c r="M16" t="b">
-        <v>1</v>
-      </c>
-      <c r="O16" t="b">
-        <v>0</v>
-      </c>
-      <c r="P16" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>1</v>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -47654,8 +49650,10 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -47677,8 +49675,10 @@
       <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -47700,8 +49700,10 @@
       <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -47723,8 +49725,10 @@
       <c r="D5" t="n">
         <v>4</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -50742,8 +52746,10 @@
           <t>ROL-01</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>3209236088</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3209236088</t>
+        </is>
       </c>
       <c r="H2" s="2" t="n">
         <v>46229</v>
@@ -50785,8 +52791,10 @@
           <t>ROL-03</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>3210123456</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3210123456</t>
+        </is>
       </c>
       <c r="H3" s="2" t="n">
         <v>46229</v>
@@ -50828,8 +52836,10 @@
           <t>ROL-03</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>3211234567</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3211234567</t>
+        </is>
       </c>
       <c r="H4" s="2" t="n">
         <v>46229</v>
@@ -50871,8 +52881,10 @@
           <t>ROL-03</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>3212345678</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3212345678</t>
+        </is>
       </c>
       <c r="H5" s="2" t="n">
         <v>46229</v>
@@ -50914,8 +52926,10 @@
           <t>ROL-03</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>3213456789</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3213456789</t>
+        </is>
       </c>
       <c r="H6" s="2" t="n">
         <v>46229</v>
@@ -50957,8 +52971,10 @@
           <t>ROL-02</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>3214567890</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3214567890</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>46229</v>
@@ -51000,8 +53016,10 @@
           <t>ROL-02</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>3215678901</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3215678901</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>46229</v>
@@ -51043,8 +53061,10 @@
           <t>ROL-02</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>3216789972</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3216789972</t>
+        </is>
       </c>
       <c r="H9" s="2" t="n">
         <v>46229</v>
@@ -51086,8 +53106,10 @@
           <t>ROL-02</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>3217901028</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3217901028</t>
+        </is>
       </c>
       <c r="H10" s="2" t="n">
         <v>46229</v>
@@ -51129,8 +53151,10 @@
           <t>ROL-02</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>3219012084</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3219012084</t>
+        </is>
       </c>
       <c r="H11" s="2" t="n">
         <v>46229</v>
@@ -51180,8 +53204,10 @@
       <c r="H12" s="2" t="n">
         <v>42943</v>
       </c>
-      <c r="I12" t="b">
-        <v>1</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -925,11 +925,15 @@
           <t>Falta de repuesto</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -943,11 +947,15 @@
           <t>Clima</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -961,11 +969,15 @@
           <t>Acceso restringido</t>
         </is>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -979,11 +991,15 @@
           <t>Riesgo para el tecnico</t>
         </is>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -997,11 +1013,15 @@
           <t>Requiere especialista</t>
         </is>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1074,8 +1094,10 @@
           <t>Error del satélite por encima del cual el cierre se marca como excepcional.</t>
         </is>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1102,8 +1124,10 @@
           <t>Distancia máxima al activo para poder cerrar.</t>
         </is>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1130,8 +1154,10 @@
           <t>Distancia máxima entre escaneo y cierre antes de reportarlo.</t>
         </is>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1454,8 +1480,10 @@
           <t>Sisga → Agua Clara</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1469,8 +1497,10 @@
           <t>Agua Clara → Sisga</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -26707,8 +26737,10 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -26737,8 +26769,10 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -26767,8 +26801,10 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -26797,8 +26833,10 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="F5" t="b">
-        <v>1</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -26827,8 +26865,10 @@
           <t>Alta</t>
         </is>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -27806,8 +27846,10 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -27824,8 +27866,10 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -27842,8 +27886,10 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -27860,8 +27906,10 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -27878,8 +27926,10 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -27896,8 +27946,10 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -27914,8 +27966,10 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="D8" t="b">
-        <v>1</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -27932,8 +27986,10 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="D9" t="b">
-        <v>1</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -27950,8 +28006,10 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="b">
-        <v>1</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -27968,8 +28026,10 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="b">
-        <v>1</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -27986,8 +28046,10 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="b">
-        <v>1</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -28004,8 +28066,10 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="b">
-        <v>1</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -28022,8 +28086,10 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="b">
-        <v>1</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -28040,8 +28106,10 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="b">
-        <v>1</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -49451,8 +49519,10 @@
           <t>Sí / No</t>
         </is>
       </c>
-      <c r="C2" t="b">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -49466,8 +49536,10 @@
           <t>Lista</t>
         </is>
       </c>
-      <c r="C3" t="b">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -49481,8 +49553,10 @@
           <t>Número</t>
         </is>
       </c>
-      <c r="C4" t="b">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -49496,8 +49570,10 @@
           <t>Texto corto</t>
         </is>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -49511,8 +49587,10 @@
           <t>Texto largo</t>
         </is>
       </c>
-      <c r="C6" t="b">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -49526,8 +49604,10 @@
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C7" t="b">
-        <v>1</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -49541,8 +49621,10 @@
           <t>Hora</t>
         </is>
       </c>
-      <c r="C8" t="b">
-        <v>1</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -49556,8 +49638,10 @@
           <t>Fotografía</t>
         </is>
       </c>
-      <c r="C9" t="b">
-        <v>1</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -49571,8 +49655,10 @@
           <t>Firma</t>
         </is>
       </c>
-      <c r="C10" t="b">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -49586,8 +49672,10 @@
           <t>GPS</t>
         </is>
       </c>
-      <c r="C11" t="b">
-        <v>1</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -52756,7 +52844,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -52801,7 +52889,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -52846,7 +52934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -52891,7 +52979,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -52936,7 +53024,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -52981,7 +53069,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -53026,7 +53114,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -53071,7 +53159,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -53116,7 +53204,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -53161,7 +53249,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -53262,8 +53350,10 @@
           <t>UNF-01</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -53282,8 +53372,10 @@
           <t>UNF-02</t>
         </is>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -53302,8 +53394,10 @@
           <t>UNF-03</t>
         </is>
       </c>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -53322,8 +53416,10 @@
           <t>UNF-04</t>
         </is>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -54509,8 +54605,10 @@
           <t>Operativo</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -54524,8 +54622,10 @@
           <t>En mantenimiento</t>
         </is>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -54539,8 +54639,10 @@
           <t>Fuera de servicio</t>
         </is>
       </c>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -54554,8 +54656,10 @@
           <t>Retirado</t>
         </is>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -54623,11 +54727,15 @@
           <t>Sistema</t>
         </is>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -54649,11 +54757,15 @@
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -54675,11 +54787,15 @@
           <t>Tecnico</t>
         </is>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -54701,11 +54817,15 @@
           <t>Tecnico</t>
         </is>
       </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -54727,11 +54847,15 @@
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -54753,11 +54877,15 @@
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -54779,11 +54907,15 @@
           <t>Sistema</t>
         </is>
       </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -54605,6 +54605,11 @@
           <t>Operativo</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -54622,6 +54627,11 @@
           <t>En mantenimiento</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -54639,6 +54649,11 @@
           <t>Fuera de servicio</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -54654,6 +54669,11 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>Retirado</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -26225,7 +26225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26281,65 +26281,60 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Precision_GPS</t>
+          <t>CierreConExcepcion</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>CierreConExcepcion</t>
+          <t>MotivoExcepcion</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>MotivoExcepcion</t>
+          <t>RequiereSegundaVisita</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>RequiereSegundaVisita</t>
+          <t>MotivoPendienteID</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>MotivoPendienteID</t>
+          <t>ModoFallaID</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ModoFallaID</t>
+          <t>Observaciones</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Observaciones</t>
+          <t>AprobadoSupervisor</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>AprobadoSupervisor</t>
+          <t>FechaAprobacion</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>FechaAprobacion</t>
+          <t>ObservacionRechazo</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ObservacionRechazo</t>
+          <t>UsuarioRegistro</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>UsuarioRegistro</t>
+          <t>FechaHoraRegistro</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>FechaHoraRegistro</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -54739,7 +54739,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -54919,7 +54919,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sistema</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -26877,7 +26877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26908,15 +26908,10 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>PrecisionGPS</t>
+          <t>FechaHora</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>FechaHora</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>Usuario</t>
         </is>

--- a/BD/Modelo_Datos_PLANTILLA.xlsx
+++ b/BD/Modelo_Datos_PLANTILLA.xlsx
@@ -840,7 +840,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>USR_Usuarios | 11 filas | Personas reales</t>
+          <t>USR_Usuarios | 12 filas | Personas reales</t>
         </is>
       </c>
     </row>
@@ -52743,7 +52743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52829,8 +52829,10 @@
           <t>3209236088</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>46229</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -52874,8 +52876,10 @@
           <t>3210123456</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
-        <v>46229</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -52919,8 +52923,10 @@
           <t>3211234567</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
-        <v>46229</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -52964,8 +52970,10 @@
           <t>3212345678</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>46229</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -53009,8 +53017,10 @@
           <t>3213456789</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>46229</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -53054,8 +53064,10 @@
           <t>3214567890</t>
         </is>
       </c>
-      <c r="H7" s="2" t="n">
-        <v>46229</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -53099,8 +53111,10 @@
           <t>3215678901</t>
         </is>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>46229</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -53144,8 +53158,10 @@
           <t>3216789972</t>
         </is>
       </c>
-      <c r="H9" s="2" t="n">
-        <v>46229</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -53189,8 +53205,10 @@
           <t>3217901028</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>46229</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -53234,8 +53252,10 @@
           <t>3219012084</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>46229</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-07-26 00:00:00</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -53279,10 +53299,59 @@
           <t>+57321654987</t>
         </is>
       </c>
-      <c r="H12" s="2" t="n">
-        <v>42943</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2017-07-27 00:00:00</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>USR-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Diego Zuniga</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>dieleoz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cuenta de pruebas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>DZ</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ROL-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>+573000000000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
